--- a/tracking_forms/026_trainee_progress_report_form_cellular_sales--tracking_forms.xlsx
+++ b/tracking_forms/026_trainee_progress_report_form_cellular_sales--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>overall_performance</t>
+          <t>Overall Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Communication Skills</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>communication_with_trainee</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>communication_with_trainee</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>skills_proficiency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>Skills Proficiency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>attitude</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>work_knowledge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>Work Knowledge</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>work_knowledge</t>
+          <t>areas_for_improvement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>work_knowledge</t>
+          <t>Areas for Improvement</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>areas_for_improvement</t>
+          <t>support_given</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>areas_for_improvement</t>
+          <t>Support Given</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>support_given</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>support_given</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>trainee_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Trainee Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>mentor_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>Mentor Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trainee_name</t>
+          <t>trainee_progress_status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>trainee_name</t>
+          <t>Trainee Progress Status</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,58 +819,58 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mentor_name</t>
+          <t>training_progress_form_id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mentor_name</t>
+          <t>Training Progress Form ID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>trainee_progress_status</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>trainee_progress_status</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>training_progress_form_id</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>training_progress_form_id</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>trainee_progress_report_status</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>trainee_progress_report_status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1136,7 +975,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1153,7 +992,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1170,14 +1009,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +1026,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,14 +1043,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1221,14 +1060,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>communication_with_trainee_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1077,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>communication_with_trainee_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1255,14 +1094,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>communication_with_trainee_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1272,14 +1111,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>skills_proficiency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1289,14 +1128,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>skills_proficiency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1306,14 +1145,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>skills_proficiency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1323,14 +1162,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>attitude_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1340,14 +1179,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>attitude_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1357,14 +1196,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>attitude_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1374,14 +1213,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>attitude_choices</t>
+          <t>work_knowledge_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1391,14 +1230,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>attitude_choices</t>
+          <t>work_knowledge_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1408,14 +1247,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>attitude_choices</t>
+          <t>work_knowledge_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1425,58 +1264,58 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_knowledge_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_knowledge_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_knowledge_choices</t>
+          <t>areas_for_improvement_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>Skills</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>attitude</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Attitude</t>
         </is>
       </c>
     </row>
@@ -1505,148 +1344,97 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>work_knowledge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>Work Knowledge</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>areas_for_improvement_choices</t>
+          <t>support_given_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>areas_for_improvement_choices</t>
+          <t>support_given_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>areas_for_improvement_choices</t>
+          <t>trainee_progress_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>work_knowledge</t>
+          <t>on_track</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>work_knowledge</t>
+          <t>On Track</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>support_given_choices</t>
+          <t>trainee_progress_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>off_track</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Off Track</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>support_given_choices</t>
+          <t>trainee_progress_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>trainee_progress_status_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>on_track</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>on_track</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>trainee_progress_status_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>off_track</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>off_track</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>trainee_progress_status_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>unknown</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
